--- a/leads.xlsx
+++ b/leads.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +973,98 @@
       <c r="V6" t="inlineStr">
         <is>
           <t>Family-owned solar energy, electrical, and roofing contractor in Auburn, NH founded in 2021 by owner Hunter Judd. Company uses 100% in-house installers (no subcontracting) and is an A+ BBB accredited business. Services include custom rooftop/ground-mounted solar panel installations, battery backup systems (Enphase storage), heat pumps, solar maintenance/repairs, roof replacements, and tree removal coordination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Manchester, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SRsolarNH/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://srsolarnh.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SRsolarNH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Josh Koehler</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>(603) 540-4243</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Josh@SRsolarNH.com</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Adrianne@SRsolarNH.com</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/SRsolarNH/index.html</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Family-owned residential and commercial solar installer based in NH, serving NH, ME, and MA. Recognized as EnergySage Installer of the Year (2025/2026). Led by founders Josh and Adrianne Koehler. Over 400 installations completed. Services include custom rooftop/ground-mount solar, Tesla Powerwall and FranklinWH battery backup, and EV charging. Direct outreach via Josh@SRsolarNH.com.</t>
         </is>
       </c>
     </row>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,19 +1052,106 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Family-owned residential and commercial solar installer based in NH, serving NH, ME, and MA. Recognized as EnergySage Installer of the Year (2025/2026). Led by founders Josh and Adrianne Koehler. Over 400 installations completed. Services include custom rooftop/ground-mount solar, Tesla Powerwall and FranklinWH battery backup, and EV charging. Direct outreach via Josh@SRsolarNH.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bow, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/granitestatesolar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/granite-state-solar</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.granitestatesolar.com</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Granite State Solar</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paul Lesure</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>(603) 369-4318</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>info@granitestatesolar.com</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/GraniteStateSolar/index.html</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Established residential and commercial solar installer based in Bow, NH. Founded in 2008 by Alan Gauntt. Led by President Paul Lesure and GM Ben Soucy. Certified Enphase Platinum installer. Offers custom design, battery backup (Tesla Powerwall), EV charging, and solar monitoring. Direct outreach via info@granitestatesolar.com.</t>
         </is>
       </c>
     </row>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,19 +1139,280 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Established residential and commercial solar installer based in Bow, NH. Founded in 2008 by Alan Gauntt. Led by President Paul Lesure and GM Ben Soucy. Certified Enphase Platinum installer. Offers custom design, battery backup (Tesla Powerwall), EV charging, and solar monitoring. Direct outreach via info@granitestatesolar.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>New Hampton, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/newhampshiresolar/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://nh.solar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>New Hampshire Solar</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Peter Hall</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>(603) 968-6031</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>peter@nh.solar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/NewHampshireSolar/index.html</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Locally owned custom solar installer based in New Hampton, NH. Founded in 2017 by owner Peter Hall. Focuses on bifacial ground-mounted solar arrays and fully off-grid systems. Restricts service area to a 30-mile radius around New Hampton. Reaches customers directly via peter@nh.solar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Roofing Company</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Laconia, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/energyshieldnh/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>http://energyshieldnh.com</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Energy Shield of New Hampshire</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>(603) 637-4827</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>info@energyshieldnh.com</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/EnergyShieldofNewHampshire/index.html</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Family-owned exterior home improvement contractor specializing in roofing (residential shingles and metal roofs) and solar energy installation. Operating for over 40 years. Led by owners Josh and Mark Crandall. Contactable at info@energyshieldnh.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Exeter, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/603solar/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://603solar.com</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>603 Solar</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Zachary Haithcock</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>(603) 570-2607</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>zach@603solar.com</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>sean@603solar.com</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>erin@603solar.com</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/603Solar/index.html</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Co-founded in 2018 by Zachary Haithcock, Sean Carlson, and Scot Johnson. Headquartered in Exeter, NH. Provides turnkey residential and commercial solar PV installations across NH, Southern ME, and Northern MA. Named #1 Solar Company in Best of the 603 and Best of the Seacoast community choice awards (2023-2025). Direct contacts: zach@603solar.com and sean@603solar.com.</t>
         </is>
       </c>
     </row>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,19 +1400,188 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Co-founded in 2018 by Zachary Haithcock, Sean Carlson, and Scot Johnson. Headquartered in Exeter, NH. Provides turnkey residential and commercial solar PV installations across NH, Southern ME, and Northern MA. Named #1 Solar Company in Best of the 603 and Best of the Seacoast community choice awards (2023-2025). Direct contacts: zach@603solar.com and sean@603solar.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brentwood, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ReVisionEnergy</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/revisionenergy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/revision-energy</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.revisionenergy.com</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ReVision Energy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Fortunat Mueller</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>(603) 679-1777</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fortunat@revisionenergy.com</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>phil@revisionenergy.com</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hello@revisionenergy.com</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/ReVisionEnergy/index.html</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Full-service 100% employee-owned solar contractor in Brentwood, NH founded in 2003 by Phil Coupe &amp; Fortunat Mueller. B-Corp certified with A+ BBB rating. 4.9 rating on Google (200+ reviews). Services include solar PV installation, Tesla Powerwall batteries, heat pumps, EV chargers. Runs in-house electrical apprenticeship school (RETC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Concord, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SundialSolarNH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sundial-solar-nh</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://sundialsolarnh.com</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sundial Solar</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ryan Young</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>(603) 961-0045</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ryan@sundialsolarnh.com</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>sales@sundialsolarnh.com</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/SundialSolar/index.html</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Full-service turnkey solar and geothermal contractor in Concord, NH active since 2015. Owned and managed by Ryan Young. Vetted EnergySage Approved installer using all in-house licensed crews instead of subcontractors. Services include solar PV installation, geothermal heating/cooling, battery backup, and heat pumps.</t>
         </is>
       </c>
     </row>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1582,6 +1582,180 @@
       <c r="V13" t="inlineStr">
         <is>
           <t>Full-service turnkey solar and geothermal contractor in Concord, NH active since 2015. Owned and managed by Ryan Young. Vetted EnergySage Approved installer using all in-house licensed crews instead of subcontractors. Services include solar PV installation, geothermal heating/cooling, battery backup, and heat pumps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Canterbury, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/seventhgensolar</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.seventhgensolar.com</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Seventh Gen Solar</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Nathan (Nate) Preisendorfer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>(603) 731-4777</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Nate@SeventhGenSolar.com</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/SeventhGenSolar/index.html</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Family-owned solar PV + electrical contractor in Canterbury/Boscawen NH (7th Gen Solar LLC). Owner: Nate Preisendorfer. Services: net-metered + off-grid solar, hybrid battery backup, EV charging, whole-home generators, mini-split AC, commercial/residential electrical. Service area: NH/ME/VT. 10+ yrs experience. Active on Facebook. Charitable: donated solar install at Veterans Memorial Recreation Area. Listed on EnergySage &amp; SolarReviews. Phone 2: (603) 717-6367.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Solar Panel Company</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Salem, New Hampshire</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Solarbyjazzi</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solarbyjazzi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://solarbyjazzi.com</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Solar By JAzzi</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Jason Azzi</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>(603) 560-3999</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>solarbyjazzi@gmail.com</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://coldemail-dun.vercel.app/coldemail/SolarByJAzzi/index.html</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Residential + commercial solar contractor in Salem NH, powered by Sunrun. Owner: Jason Azzi (20+ yrs solar experience, ex-Fortune 500 / Sunrun). Services: solar PV install, battery storage, zero-down financing. 5.0 Google rating (16 reviews). Service area: most of New England. Active community networker (RCAMA sponsor, church publications). SM managed by FiveChain Marketing. Handle @solarbyjazzi. Hours: M-F 8am-6pm, Sat-Sun 8am-5pm.</t>
         </is>
       </c>
     </row>
